--- a/files/temp_files/statement_2026_04.xlsx
+++ b/files/temp_files/statement_2026_04.xlsx
@@ -594,7 +594,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>21.39</v>
+        <v>-21.39</v>
       </c>
       <c r="D2" t="s">
         <v>58</v>
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>373.89</v>
+        <v>-373.89</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -636,7 +636,7 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>60.04</v>
+        <v>-60.04</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -650,7 +650,7 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>178.88</v>
+        <v>-178.88</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
@@ -664,7 +664,7 @@
         <v>39</v>
       </c>
       <c r="C7">
-        <v>56.56</v>
+        <v>-56.56</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
@@ -678,7 +678,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>534.21</v>
+        <v>-534.21</v>
       </c>
       <c r="D8" t="s">
         <v>59</v>
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C9">
-        <v>100.1</v>
+        <v>-100.1</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
@@ -706,7 +706,7 @@
         <v>40</v>
       </c>
       <c r="C10">
-        <v>646.9400000000001</v>
+        <v>-646.9400000000001</v>
       </c>
       <c r="D10" t="s">
         <v>59</v>
@@ -720,7 +720,7 @@
         <v>39</v>
       </c>
       <c r="C11">
-        <v>112.13</v>
+        <v>-112.13</v>
       </c>
       <c r="D11" t="s">
         <v>63</v>
@@ -734,7 +734,7 @@
         <v>42</v>
       </c>
       <c r="C12">
-        <v>368.19</v>
+        <v>-368.19</v>
       </c>
       <c r="D12" t="s">
         <v>64</v>
@@ -748,7 +748,7 @@
         <v>43</v>
       </c>
       <c r="C13">
-        <v>13.79</v>
+        <v>-13.79</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
@@ -776,7 +776,7 @@
         <v>44</v>
       </c>
       <c r="C15">
-        <v>282.91</v>
+        <v>-282.91</v>
       </c>
       <c r="D15" t="s">
         <v>63</v>
@@ -790,7 +790,7 @@
         <v>39</v>
       </c>
       <c r="C16">
-        <v>68.48999999999999</v>
+        <v>-68.48999999999999</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -804,7 +804,7 @@
         <v>45</v>
       </c>
       <c r="C17">
-        <v>230.81</v>
+        <v>-230.81</v>
       </c>
       <c r="D17" t="s">
         <v>64</v>
@@ -818,7 +818,7 @@
         <v>40</v>
       </c>
       <c r="C18">
-        <v>734.72</v>
+        <v>-734.72</v>
       </c>
       <c r="D18" t="s">
         <v>59</v>
@@ -832,7 +832,7 @@
         <v>46</v>
       </c>
       <c r="C19">
-        <v>148.59</v>
+        <v>-148.59</v>
       </c>
       <c r="D19" t="s">
         <v>64</v>
@@ -846,7 +846,7 @@
         <v>42</v>
       </c>
       <c r="C20">
-        <v>163.2</v>
+        <v>-163.2</v>
       </c>
       <c r="D20" t="s">
         <v>64</v>
@@ -860,7 +860,7 @@
         <v>37</v>
       </c>
       <c r="C21">
-        <v>105.95</v>
+        <v>-105.95</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -874,7 +874,7 @@
         <v>35</v>
       </c>
       <c r="C22">
-        <v>290.44</v>
+        <v>-290.44</v>
       </c>
       <c r="D22" t="s">
         <v>59</v>
@@ -888,7 +888,7 @@
         <v>47</v>
       </c>
       <c r="C23">
-        <v>72.17</v>
+        <v>-72.17</v>
       </c>
       <c r="D23" t="s">
         <v>65</v>
@@ -902,7 +902,7 @@
         <v>48</v>
       </c>
       <c r="C24">
-        <v>79.31999999999999</v>
+        <v>-79.31999999999999</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -916,7 +916,7 @@
         <v>49</v>
       </c>
       <c r="C25">
-        <v>10.98</v>
+        <v>-10.98</v>
       </c>
       <c r="D25" t="s">
         <v>58</v>
@@ -930,7 +930,7 @@
         <v>50</v>
       </c>
       <c r="C26">
-        <v>44.64</v>
+        <v>-44.64</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -944,7 +944,7 @@
         <v>35</v>
       </c>
       <c r="C27">
-        <v>641.15</v>
+        <v>-641.15</v>
       </c>
       <c r="D27" t="s">
         <v>59</v>
@@ -958,7 +958,7 @@
         <v>43</v>
       </c>
       <c r="C28">
-        <v>13.75</v>
+        <v>-13.75</v>
       </c>
       <c r="D28" t="s">
         <v>58</v>
@@ -972,7 +972,7 @@
         <v>51</v>
       </c>
       <c r="C29">
-        <v>600.76</v>
+        <v>-600.76</v>
       </c>
       <c r="D29" t="s">
         <v>59</v>
@@ -986,7 +986,7 @@
         <v>50</v>
       </c>
       <c r="C30">
-        <v>229.81</v>
+        <v>-229.81</v>
       </c>
       <c r="D30" t="s">
         <v>63</v>
@@ -1000,7 +1000,7 @@
         <v>38</v>
       </c>
       <c r="C31">
-        <v>159.4</v>
+        <v>-159.4</v>
       </c>
       <c r="D31" t="s">
         <v>62</v>
@@ -1014,7 +1014,7 @@
         <v>35</v>
       </c>
       <c r="C32">
-        <v>80.06999999999999</v>
+        <v>-80.06999999999999</v>
       </c>
       <c r="D32" t="s">
         <v>59</v>
@@ -1042,7 +1042,7 @@
         <v>46</v>
       </c>
       <c r="C34">
-        <v>30.09</v>
+        <v>-30.09</v>
       </c>
       <c r="D34" t="s">
         <v>64</v>
@@ -1056,7 +1056,7 @@
         <v>39</v>
       </c>
       <c r="C35">
-        <v>252.68</v>
+        <v>-252.68</v>
       </c>
       <c r="D35" t="s">
         <v>63</v>
@@ -1070,7 +1070,7 @@
         <v>42</v>
       </c>
       <c r="C36">
-        <v>380.72</v>
+        <v>-380.72</v>
       </c>
       <c r="D36" t="s">
         <v>64</v>
@@ -1084,7 +1084,7 @@
         <v>38</v>
       </c>
       <c r="C37">
-        <v>159.53</v>
+        <v>-159.53</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -1098,7 +1098,7 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>48.75</v>
+        <v>-48.75</v>
       </c>
       <c r="D38" t="s">
         <v>58</v>
@@ -1126,7 +1126,7 @@
         <v>49</v>
       </c>
       <c r="C40">
-        <v>27.97</v>
+        <v>-27.97</v>
       </c>
       <c r="D40" t="s">
         <v>58</v>
@@ -1140,7 +1140,7 @@
         <v>43</v>
       </c>
       <c r="C41">
-        <v>30.53</v>
+        <v>-30.53</v>
       </c>
       <c r="D41" t="s">
         <v>58</v>
@@ -1154,7 +1154,7 @@
         <v>52</v>
       </c>
       <c r="C42">
-        <v>67.89</v>
+        <v>-67.89</v>
       </c>
       <c r="D42" t="s">
         <v>62</v>
@@ -1168,7 +1168,7 @@
         <v>53</v>
       </c>
       <c r="C43">
-        <v>71.94</v>
+        <v>-71.94</v>
       </c>
       <c r="D43" t="s">
         <v>61</v>
@@ -1182,7 +1182,7 @@
         <v>52</v>
       </c>
       <c r="C44">
-        <v>122.75</v>
+        <v>-122.75</v>
       </c>
       <c r="D44" t="s">
         <v>62</v>
@@ -1196,7 +1196,7 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>105.32</v>
+        <v>-105.32</v>
       </c>
       <c r="D45" t="s">
         <v>63</v>
@@ -1224,7 +1224,7 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>22</v>
+        <v>-22</v>
       </c>
       <c r="D47" t="s">
         <v>65</v>
@@ -1238,7 +1238,7 @@
         <v>48</v>
       </c>
       <c r="C48">
-        <v>14.41</v>
+        <v>-14.41</v>
       </c>
       <c r="D48" t="s">
         <v>65</v>
@@ -1252,7 +1252,7 @@
         <v>53</v>
       </c>
       <c r="C49">
-        <v>56.94</v>
+        <v>-56.94</v>
       </c>
       <c r="D49" t="s">
         <v>61</v>
@@ -1266,7 +1266,7 @@
         <v>53</v>
       </c>
       <c r="C50">
-        <v>66.77</v>
+        <v>-66.77</v>
       </c>
       <c r="D50" t="s">
         <v>61</v>
@@ -1280,7 +1280,7 @@
         <v>41</v>
       </c>
       <c r="C51">
-        <v>63.33</v>
+        <v>-63.33</v>
       </c>
       <c r="D51" t="s">
         <v>61</v>
@@ -1294,7 +1294,7 @@
         <v>45</v>
       </c>
       <c r="C52">
-        <v>144.85</v>
+        <v>-144.85</v>
       </c>
       <c r="D52" t="s">
         <v>64</v>
@@ -1308,7 +1308,7 @@
         <v>37</v>
       </c>
       <c r="C53">
-        <v>146.48</v>
+        <v>-146.48</v>
       </c>
       <c r="D53" t="s">
         <v>61</v>
@@ -1322,7 +1322,7 @@
         <v>47</v>
       </c>
       <c r="C54">
-        <v>23.67</v>
+        <v>-23.67</v>
       </c>
       <c r="D54" t="s">
         <v>65</v>
@@ -1336,7 +1336,7 @@
         <v>48</v>
       </c>
       <c r="C55">
-        <v>31.39</v>
+        <v>-31.39</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
@@ -1350,7 +1350,7 @@
         <v>48</v>
       </c>
       <c r="C56">
-        <v>72.75</v>
+        <v>-72.75</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -1378,7 +1378,7 @@
         <v>51</v>
       </c>
       <c r="C58">
-        <v>570.42</v>
+        <v>-570.42</v>
       </c>
       <c r="D58" t="s">
         <v>59</v>
@@ -1392,7 +1392,7 @@
         <v>44</v>
       </c>
       <c r="C59">
-        <v>234.6</v>
+        <v>-234.6</v>
       </c>
       <c r="D59" t="s">
         <v>63</v>
@@ -1406,7 +1406,7 @@
         <v>38</v>
       </c>
       <c r="C60">
-        <v>29.76</v>
+        <v>-29.76</v>
       </c>
       <c r="D60" t="s">
         <v>62</v>
@@ -1420,7 +1420,7 @@
         <v>37</v>
       </c>
       <c r="C61">
-        <v>66.04000000000001</v>
+        <v>-66.04000000000001</v>
       </c>
       <c r="D61" t="s">
         <v>61</v>
@@ -1434,7 +1434,7 @@
         <v>42</v>
       </c>
       <c r="C62">
-        <v>337.68</v>
+        <v>-337.68</v>
       </c>
       <c r="D62" t="s">
         <v>64</v>
@@ -1448,7 +1448,7 @@
         <v>57</v>
       </c>
       <c r="C63">
-        <v>138.44</v>
+        <v>-138.44</v>
       </c>
       <c r="D63" t="s">
         <v>62</v>
@@ -1462,7 +1462,7 @@
         <v>45</v>
       </c>
       <c r="C64">
-        <v>10.78</v>
+        <v>-10.78</v>
       </c>
       <c r="D64" t="s">
         <v>64</v>
@@ -1476,7 +1476,7 @@
         <v>43</v>
       </c>
       <c r="C65">
-        <v>49.01</v>
+        <v>-49.01</v>
       </c>
       <c r="D65" t="s">
         <v>58</v>
@@ -1490,7 +1490,7 @@
         <v>47</v>
       </c>
       <c r="C66">
-        <v>48.59</v>
+        <v>-48.59</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -1504,7 +1504,7 @@
         <v>57</v>
       </c>
       <c r="C67">
-        <v>63.13</v>
+        <v>-63.13</v>
       </c>
       <c r="D67" t="s">
         <v>62</v>
@@ -1518,7 +1518,7 @@
         <v>49</v>
       </c>
       <c r="C68">
-        <v>20.93</v>
+        <v>-20.93</v>
       </c>
       <c r="D68" t="s">
         <v>58</v>
@@ -1532,7 +1532,7 @@
         <v>52</v>
       </c>
       <c r="C69">
-        <v>66.76000000000001</v>
+        <v>-66.76000000000001</v>
       </c>
       <c r="D69" t="s">
         <v>62</v>
@@ -1546,7 +1546,7 @@
         <v>47</v>
       </c>
       <c r="C70">
-        <v>63.56</v>
+        <v>-63.56</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -1560,7 +1560,7 @@
         <v>40</v>
       </c>
       <c r="C71">
-        <v>467.59</v>
+        <v>-467.59</v>
       </c>
       <c r="D71" t="s">
         <v>59</v>
@@ -1602,7 +1602,7 @@
         <v>57</v>
       </c>
       <c r="C74">
-        <v>195.95</v>
+        <v>-195.95</v>
       </c>
       <c r="D74" t="s">
         <v>62</v>
@@ -1616,7 +1616,7 @@
         <v>41</v>
       </c>
       <c r="C75">
-        <v>147.76</v>
+        <v>-147.76</v>
       </c>
       <c r="D75" t="s">
         <v>61</v>
@@ -1630,7 +1630,7 @@
         <v>57</v>
       </c>
       <c r="C76">
-        <v>87.98</v>
+        <v>-87.98</v>
       </c>
       <c r="D76" t="s">
         <v>62</v>
@@ -1644,7 +1644,7 @@
         <v>43</v>
       </c>
       <c r="C77">
-        <v>29.66</v>
+        <v>-29.66</v>
       </c>
       <c r="D77" t="s">
         <v>58</v>
@@ -1672,7 +1672,7 @@
         <v>38</v>
       </c>
       <c r="C79">
-        <v>34.49</v>
+        <v>-34.49</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
@@ -1700,7 +1700,7 @@
         <v>35</v>
       </c>
       <c r="C81">
-        <v>509.01</v>
+        <v>-509.01</v>
       </c>
       <c r="D81" t="s">
         <v>59</v>
@@ -1714,7 +1714,7 @@
         <v>43</v>
       </c>
       <c r="C82">
-        <v>38.13</v>
+        <v>-38.13</v>
       </c>
       <c r="D82" t="s">
         <v>58</v>
@@ -1728,7 +1728,7 @@
         <v>52</v>
       </c>
       <c r="C83">
-        <v>61.08</v>
+        <v>-61.08</v>
       </c>
       <c r="D83" t="s">
         <v>62</v>
@@ -1742,7 +1742,7 @@
         <v>46</v>
       </c>
       <c r="C84">
-        <v>227.13</v>
+        <v>-227.13</v>
       </c>
       <c r="D84" t="s">
         <v>64</v>
@@ -1756,7 +1756,7 @@
         <v>44</v>
       </c>
       <c r="C85">
-        <v>133.82</v>
+        <v>-133.82</v>
       </c>
       <c r="D85" t="s">
         <v>63</v>
@@ -1770,7 +1770,7 @@
         <v>43</v>
       </c>
       <c r="C86">
-        <v>42.23</v>
+        <v>-42.23</v>
       </c>
       <c r="D86" t="s">
         <v>58</v>
@@ -1784,7 +1784,7 @@
         <v>44</v>
       </c>
       <c r="C87">
-        <v>163.11</v>
+        <v>-163.11</v>
       </c>
       <c r="D87" t="s">
         <v>63</v>
@@ -1798,7 +1798,7 @@
         <v>39</v>
       </c>
       <c r="C88">
-        <v>278.8</v>
+        <v>-278.8</v>
       </c>
       <c r="D88" t="s">
         <v>63</v>
@@ -1812,7 +1812,7 @@
         <v>51</v>
       </c>
       <c r="C89">
-        <v>493.73</v>
+        <v>-493.73</v>
       </c>
       <c r="D89" t="s">
         <v>59</v>
@@ -1826,7 +1826,7 @@
         <v>45</v>
       </c>
       <c r="C90">
-        <v>6.32</v>
+        <v>-6.32</v>
       </c>
       <c r="D90" t="s">
         <v>64</v>
@@ -1840,7 +1840,7 @@
         <v>51</v>
       </c>
       <c r="C91">
-        <v>952.99</v>
+        <v>-952.99</v>
       </c>
       <c r="D91" t="s">
         <v>59</v>
@@ -1854,7 +1854,7 @@
         <v>49</v>
       </c>
       <c r="C92">
-        <v>9.380000000000001</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D92" t="s">
         <v>58</v>
@@ -1868,7 +1868,7 @@
         <v>42</v>
       </c>
       <c r="C93">
-        <v>157.53</v>
+        <v>-157.53</v>
       </c>
       <c r="D93" t="s">
         <v>64</v>
@@ -1882,7 +1882,7 @@
         <v>52</v>
       </c>
       <c r="C94">
-        <v>171.19</v>
+        <v>-171.19</v>
       </c>
       <c r="D94" t="s">
         <v>62</v>
@@ -1896,7 +1896,7 @@
         <v>49</v>
       </c>
       <c r="C95">
-        <v>29.16</v>
+        <v>-29.16</v>
       </c>
       <c r="D95" t="s">
         <v>58</v>
@@ -1910,7 +1910,7 @@
         <v>43</v>
       </c>
       <c r="C96">
-        <v>5.28</v>
+        <v>-5.28</v>
       </c>
       <c r="D96" t="s">
         <v>58</v>
@@ -1924,7 +1924,7 @@
         <v>41</v>
       </c>
       <c r="C97">
-        <v>62.07</v>
+        <v>-62.07</v>
       </c>
       <c r="D97" t="s">
         <v>61</v>
@@ -1938,7 +1938,7 @@
         <v>38</v>
       </c>
       <c r="C98">
-        <v>97.63</v>
+        <v>-97.63</v>
       </c>
       <c r="D98" t="s">
         <v>62</v>
@@ -1952,7 +1952,7 @@
         <v>43</v>
       </c>
       <c r="C99">
-        <v>30.71</v>
+        <v>-30.71</v>
       </c>
       <c r="D99" t="s">
         <v>58</v>
@@ -1966,7 +1966,7 @@
         <v>37</v>
       </c>
       <c r="C100">
-        <v>92.55</v>
+        <v>-92.55</v>
       </c>
       <c r="D100" t="s">
         <v>61</v>
@@ -1980,7 +1980,7 @@
         <v>43</v>
       </c>
       <c r="C101">
-        <v>42.24</v>
+        <v>-42.24</v>
       </c>
       <c r="D101" t="s">
         <v>58</v>
@@ -1994,7 +1994,7 @@
         <v>40</v>
       </c>
       <c r="C102">
-        <v>994.45</v>
+        <v>-994.45</v>
       </c>
       <c r="D102" t="s">
         <v>59</v>
@@ -2008,7 +2008,7 @@
         <v>42</v>
       </c>
       <c r="C103">
-        <v>399.13</v>
+        <v>-399.13</v>
       </c>
       <c r="D103" t="s">
         <v>64</v>
@@ -2022,7 +2022,7 @@
         <v>40</v>
       </c>
       <c r="C104">
-        <v>556.16</v>
+        <v>-556.16</v>
       </c>
       <c r="D104" t="s">
         <v>59</v>
@@ -2036,7 +2036,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>190.12</v>
+        <v>-190.12</v>
       </c>
       <c r="D105" t="s">
         <v>63</v>
@@ -2050,7 +2050,7 @@
         <v>44</v>
       </c>
       <c r="C106">
-        <v>67.93000000000001</v>
+        <v>-67.93000000000001</v>
       </c>
       <c r="D106" t="s">
         <v>63</v>
@@ -2064,7 +2064,7 @@
         <v>42</v>
       </c>
       <c r="C107">
-        <v>11.06</v>
+        <v>-11.06</v>
       </c>
       <c r="D107" t="s">
         <v>64</v>
@@ -2078,7 +2078,7 @@
         <v>48</v>
       </c>
       <c r="C108">
-        <v>63.58</v>
+        <v>-63.58</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
@@ -2092,7 +2092,7 @@
         <v>52</v>
       </c>
       <c r="C109">
-        <v>110.04</v>
+        <v>-110.04</v>
       </c>
       <c r="D109" t="s">
         <v>62</v>
@@ -2106,7 +2106,7 @@
         <v>51</v>
       </c>
       <c r="C110">
-        <v>765.86</v>
+        <v>-765.86</v>
       </c>
       <c r="D110" t="s">
         <v>59</v>
@@ -2120,7 +2120,7 @@
         <v>47</v>
       </c>
       <c r="C111">
-        <v>58.66</v>
+        <v>-58.66</v>
       </c>
       <c r="D111" t="s">
         <v>65</v>
@@ -2148,7 +2148,7 @@
         <v>37</v>
       </c>
       <c r="C113">
-        <v>96.01000000000001</v>
+        <v>-96.01000000000001</v>
       </c>
       <c r="D113" t="s">
         <v>61</v>
@@ -2162,7 +2162,7 @@
         <v>45</v>
       </c>
       <c r="C114">
-        <v>121.15</v>
+        <v>-121.15</v>
       </c>
       <c r="D114" t="s">
         <v>64</v>
@@ -2176,7 +2176,7 @@
         <v>38</v>
       </c>
       <c r="C115">
-        <v>11.93</v>
+        <v>-11.93</v>
       </c>
       <c r="D115" t="s">
         <v>62</v>
@@ -2190,7 +2190,7 @@
         <v>57</v>
       </c>
       <c r="C116">
-        <v>106.96</v>
+        <v>-106.96</v>
       </c>
       <c r="D116" t="s">
         <v>62</v>
@@ -2218,7 +2218,7 @@
         <v>55</v>
       </c>
       <c r="C118">
-        <v>84.2</v>
+        <v>-84.2</v>
       </c>
       <c r="D118" t="s">
         <v>65</v>
@@ -2232,7 +2232,7 @@
         <v>45</v>
       </c>
       <c r="C119">
-        <v>136.73</v>
+        <v>-136.73</v>
       </c>
       <c r="D119" t="s">
         <v>64</v>
@@ -2246,7 +2246,7 @@
         <v>43</v>
       </c>
       <c r="C120">
-        <v>25.55</v>
+        <v>-25.55</v>
       </c>
       <c r="D120" t="s">
         <v>58</v>
@@ -2260,7 +2260,7 @@
         <v>50</v>
       </c>
       <c r="C121">
-        <v>133.45</v>
+        <v>-133.45</v>
       </c>
       <c r="D121" t="s">
         <v>63</v>
@@ -2274,7 +2274,7 @@
         <v>47</v>
       </c>
       <c r="C122">
-        <v>66.69</v>
+        <v>-66.69</v>
       </c>
       <c r="D122" t="s">
         <v>65</v>
@@ -2288,7 +2288,7 @@
         <v>38</v>
       </c>
       <c r="C123">
-        <v>33.28</v>
+        <v>-33.28</v>
       </c>
       <c r="D123" t="s">
         <v>62</v>
@@ -2302,7 +2302,7 @@
         <v>42</v>
       </c>
       <c r="C124">
-        <v>210.73</v>
+        <v>-210.73</v>
       </c>
       <c r="D124" t="s">
         <v>64</v>
@@ -2316,7 +2316,7 @@
         <v>53</v>
       </c>
       <c r="C125">
-        <v>57.59</v>
+        <v>-57.59</v>
       </c>
       <c r="D125" t="s">
         <v>61</v>
@@ -2330,7 +2330,7 @@
         <v>34</v>
       </c>
       <c r="C126">
-        <v>16.83</v>
+        <v>-16.83</v>
       </c>
       <c r="D126" t="s">
         <v>58</v>
@@ -2344,7 +2344,7 @@
         <v>57</v>
       </c>
       <c r="C127">
-        <v>155.46</v>
+        <v>-155.46</v>
       </c>
       <c r="D127" t="s">
         <v>62</v>
@@ -2358,7 +2358,7 @@
         <v>53</v>
       </c>
       <c r="C128">
-        <v>111.28</v>
+        <v>-111.28</v>
       </c>
       <c r="D128" t="s">
         <v>61</v>
@@ -2372,7 +2372,7 @@
         <v>44</v>
       </c>
       <c r="C129">
-        <v>210.75</v>
+        <v>-210.75</v>
       </c>
       <c r="D129" t="s">
         <v>63</v>
@@ -2386,7 +2386,7 @@
         <v>53</v>
       </c>
       <c r="C130">
-        <v>95.04000000000001</v>
+        <v>-95.04000000000001</v>
       </c>
       <c r="D130" t="s">
         <v>61</v>
@@ -2400,7 +2400,7 @@
         <v>47</v>
       </c>
       <c r="C131">
-        <v>43.48</v>
+        <v>-43.48</v>
       </c>
       <c r="D131" t="s">
         <v>65</v>
@@ -2414,7 +2414,7 @@
         <v>46</v>
       </c>
       <c r="C132">
-        <v>195.81</v>
+        <v>-195.81</v>
       </c>
       <c r="D132" t="s">
         <v>64</v>
@@ -2428,7 +2428,7 @@
         <v>46</v>
       </c>
       <c r="C133">
-        <v>231.45</v>
+        <v>-231.45</v>
       </c>
       <c r="D133" t="s">
         <v>64</v>
@@ -2442,7 +2442,7 @@
         <v>40</v>
       </c>
       <c r="C134">
-        <v>856.53</v>
+        <v>-856.53</v>
       </c>
       <c r="D134" t="s">
         <v>59</v>
@@ -2456,7 +2456,7 @@
         <v>52</v>
       </c>
       <c r="C135">
-        <v>59.27</v>
+        <v>-59.27</v>
       </c>
       <c r="D135" t="s">
         <v>62</v>
@@ -2470,7 +2470,7 @@
         <v>34</v>
       </c>
       <c r="C136">
-        <v>27.34</v>
+        <v>-27.34</v>
       </c>
       <c r="D136" t="s">
         <v>58</v>
@@ -2484,7 +2484,7 @@
         <v>43</v>
       </c>
       <c r="C137">
-        <v>30.51</v>
+        <v>-30.51</v>
       </c>
       <c r="D137" t="s">
         <v>58</v>
@@ -2498,7 +2498,7 @@
         <v>47</v>
       </c>
       <c r="C138">
-        <v>15.19</v>
+        <v>-15.19</v>
       </c>
       <c r="D138" t="s">
         <v>65</v>
@@ -2512,7 +2512,7 @@
         <v>44</v>
       </c>
       <c r="C139">
-        <v>96.34</v>
+        <v>-96.34</v>
       </c>
       <c r="D139" t="s">
         <v>63</v>
@@ -2526,7 +2526,7 @@
         <v>40</v>
       </c>
       <c r="C140">
-        <v>837.73</v>
+        <v>-837.73</v>
       </c>
       <c r="D140" t="s">
         <v>59</v>
@@ -2540,7 +2540,7 @@
         <v>40</v>
       </c>
       <c r="C141">
-        <v>682.84</v>
+        <v>-682.84</v>
       </c>
       <c r="D141" t="s">
         <v>59</v>
@@ -2554,7 +2554,7 @@
         <v>35</v>
       </c>
       <c r="C142">
-        <v>910.9299999999999</v>
+        <v>-910.9299999999999</v>
       </c>
       <c r="D142" t="s">
         <v>59</v>
@@ -2568,7 +2568,7 @@
         <v>43</v>
       </c>
       <c r="C143">
-        <v>30.91</v>
+        <v>-30.91</v>
       </c>
       <c r="D143" t="s">
         <v>58</v>
@@ -2582,7 +2582,7 @@
         <v>47</v>
       </c>
       <c r="C144">
-        <v>29.45</v>
+        <v>-29.45</v>
       </c>
       <c r="D144" t="s">
         <v>65</v>
@@ -2596,7 +2596,7 @@
         <v>38</v>
       </c>
       <c r="C145">
-        <v>184.46</v>
+        <v>-184.46</v>
       </c>
       <c r="D145" t="s">
         <v>62</v>
@@ -2610,7 +2610,7 @@
         <v>42</v>
       </c>
       <c r="C146">
-        <v>438.66</v>
+        <v>-438.66</v>
       </c>
       <c r="D146" t="s">
         <v>64</v>
@@ -2638,7 +2638,7 @@
         <v>34</v>
       </c>
       <c r="C148">
-        <v>26.13</v>
+        <v>-26.13</v>
       </c>
       <c r="D148" t="s">
         <v>58</v>
@@ -2652,7 +2652,7 @@
         <v>46</v>
       </c>
       <c r="C149">
-        <v>197.51</v>
+        <v>-197.51</v>
       </c>
       <c r="D149" t="s">
         <v>64</v>
@@ -2666,7 +2666,7 @@
         <v>49</v>
       </c>
       <c r="C150">
-        <v>4.6</v>
+        <v>-4.6</v>
       </c>
       <c r="D150" t="s">
         <v>58</v>
@@ -2680,7 +2680,7 @@
         <v>39</v>
       </c>
       <c r="C151">
-        <v>38.79</v>
+        <v>-38.79</v>
       </c>
       <c r="D151" t="s">
         <v>63</v>
@@ -2694,7 +2694,7 @@
         <v>47</v>
       </c>
       <c r="C152">
-        <v>83.45999999999999</v>
+        <v>-83.45999999999999</v>
       </c>
       <c r="D152" t="s">
         <v>65</v>
@@ -2708,7 +2708,7 @@
         <v>57</v>
       </c>
       <c r="C153">
-        <v>52.49</v>
+        <v>-52.49</v>
       </c>
       <c r="D153" t="s">
         <v>62</v>
@@ -2722,7 +2722,7 @@
         <v>55</v>
       </c>
       <c r="C154">
-        <v>74.56</v>
+        <v>-74.56</v>
       </c>
       <c r="D154" t="s">
         <v>65</v>
@@ -2736,7 +2736,7 @@
         <v>42</v>
       </c>
       <c r="C155">
-        <v>281.57</v>
+        <v>-281.57</v>
       </c>
       <c r="D155" t="s">
         <v>64</v>
@@ -2750,7 +2750,7 @@
         <v>50</v>
       </c>
       <c r="C156">
-        <v>242.34</v>
+        <v>-242.34</v>
       </c>
       <c r="D156" t="s">
         <v>63</v>
@@ -2764,7 +2764,7 @@
         <v>38</v>
       </c>
       <c r="C157">
-        <v>34.09</v>
+        <v>-34.09</v>
       </c>
       <c r="D157" t="s">
         <v>62</v>
@@ -2778,7 +2778,7 @@
         <v>55</v>
       </c>
       <c r="C158">
-        <v>89.76000000000001</v>
+        <v>-89.76000000000001</v>
       </c>
       <c r="D158" t="s">
         <v>65</v>
@@ -2792,7 +2792,7 @@
         <v>52</v>
       </c>
       <c r="C159">
-        <v>89.09999999999999</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="D159" t="s">
         <v>62</v>
@@ -2848,7 +2848,7 @@
         <v>41</v>
       </c>
       <c r="C163">
-        <v>62.72</v>
+        <v>-62.72</v>
       </c>
       <c r="D163" t="s">
         <v>61</v>
@@ -2862,7 +2862,7 @@
         <v>42</v>
       </c>
       <c r="C164">
-        <v>307.49</v>
+        <v>-307.49</v>
       </c>
       <c r="D164" t="s">
         <v>64</v>
@@ -2876,7 +2876,7 @@
         <v>46</v>
       </c>
       <c r="C165">
-        <v>65.14</v>
+        <v>-65.14</v>
       </c>
       <c r="D165" t="s">
         <v>64</v>
@@ -2890,7 +2890,7 @@
         <v>46</v>
       </c>
       <c r="C166">
-        <v>304.52</v>
+        <v>-304.52</v>
       </c>
       <c r="D166" t="s">
         <v>64</v>
@@ -2904,7 +2904,7 @@
         <v>47</v>
       </c>
       <c r="C167">
-        <v>22.47</v>
+        <v>-22.47</v>
       </c>
       <c r="D167" t="s">
         <v>65</v>
@@ -2932,7 +2932,7 @@
         <v>35</v>
       </c>
       <c r="C169">
-        <v>740.13</v>
+        <v>-740.13</v>
       </c>
       <c r="D169" t="s">
         <v>59</v>
@@ -2946,7 +2946,7 @@
         <v>37</v>
       </c>
       <c r="C170">
-        <v>45.42</v>
+        <v>-45.42</v>
       </c>
       <c r="D170" t="s">
         <v>61</v>
@@ -2960,7 +2960,7 @@
         <v>40</v>
       </c>
       <c r="C171">
-        <v>563.75</v>
+        <v>-563.75</v>
       </c>
       <c r="D171" t="s">
         <v>59</v>
@@ -2974,7 +2974,7 @@
         <v>43</v>
       </c>
       <c r="C172">
-        <v>5.01</v>
+        <v>-5.01</v>
       </c>
       <c r="D172" t="s">
         <v>58</v>
@@ -3002,7 +3002,7 @@
         <v>55</v>
       </c>
       <c r="C174">
-        <v>72.09</v>
+        <v>-72.09</v>
       </c>
       <c r="D174" t="s">
         <v>65</v>
@@ -3016,7 +3016,7 @@
         <v>35</v>
       </c>
       <c r="C175">
-        <v>460.51</v>
+        <v>-460.51</v>
       </c>
       <c r="D175" t="s">
         <v>59</v>
@@ -3030,7 +3030,7 @@
         <v>49</v>
       </c>
       <c r="C176">
-        <v>21.48</v>
+        <v>-21.48</v>
       </c>
       <c r="D176" t="s">
         <v>58</v>
@@ -3044,7 +3044,7 @@
         <v>52</v>
       </c>
       <c r="C177">
-        <v>190.38</v>
+        <v>-190.38</v>
       </c>
       <c r="D177" t="s">
         <v>62</v>
@@ -3058,7 +3058,7 @@
         <v>48</v>
       </c>
       <c r="C178">
-        <v>87.88</v>
+        <v>-87.88</v>
       </c>
       <c r="D178" t="s">
         <v>65</v>
@@ -3072,7 +3072,7 @@
         <v>43</v>
       </c>
       <c r="C179">
-        <v>35.52</v>
+        <v>-35.52</v>
       </c>
       <c r="D179" t="s">
         <v>58</v>
@@ -3086,7 +3086,7 @@
         <v>47</v>
       </c>
       <c r="C180">
-        <v>63.94</v>
+        <v>-63.94</v>
       </c>
       <c r="D180" t="s">
         <v>65</v>
@@ -3114,7 +3114,7 @@
         <v>44</v>
       </c>
       <c r="C182">
-        <v>92</v>
+        <v>-92</v>
       </c>
       <c r="D182" t="s">
         <v>63</v>
@@ -3128,7 +3128,7 @@
         <v>53</v>
       </c>
       <c r="C183">
-        <v>124.49</v>
+        <v>-124.49</v>
       </c>
       <c r="D183" t="s">
         <v>61</v>
@@ -3142,7 +3142,7 @@
         <v>52</v>
       </c>
       <c r="C184">
-        <v>183.26</v>
+        <v>-183.26</v>
       </c>
       <c r="D184" t="s">
         <v>62</v>
@@ -3156,7 +3156,7 @@
         <v>45</v>
       </c>
       <c r="C185">
-        <v>112.95</v>
+        <v>-112.95</v>
       </c>
       <c r="D185" t="s">
         <v>64</v>
@@ -3170,7 +3170,7 @@
         <v>34</v>
       </c>
       <c r="C186">
-        <v>26.07</v>
+        <v>-26.07</v>
       </c>
       <c r="D186" t="s">
         <v>58</v>
@@ -3184,7 +3184,7 @@
         <v>51</v>
       </c>
       <c r="C187">
-        <v>360.42</v>
+        <v>-360.42</v>
       </c>
       <c r="D187" t="s">
         <v>59</v>
@@ -3198,7 +3198,7 @@
         <v>39</v>
       </c>
       <c r="C188">
-        <v>43.05</v>
+        <v>-43.05</v>
       </c>
       <c r="D188" t="s">
         <v>63</v>
@@ -3212,7 +3212,7 @@
         <v>52</v>
       </c>
       <c r="C189">
-        <v>83.3</v>
+        <v>-83.3</v>
       </c>
       <c r="D189" t="s">
         <v>62</v>
@@ -3226,7 +3226,7 @@
         <v>48</v>
       </c>
       <c r="C190">
-        <v>23.74</v>
+        <v>-23.74</v>
       </c>
       <c r="D190" t="s">
         <v>65</v>
@@ -3240,7 +3240,7 @@
         <v>40</v>
       </c>
       <c r="C191">
-        <v>875.17</v>
+        <v>-875.17</v>
       </c>
       <c r="D191" t="s">
         <v>59</v>
@@ -3254,7 +3254,7 @@
         <v>39</v>
       </c>
       <c r="C192">
-        <v>122.05</v>
+        <v>-122.05</v>
       </c>
       <c r="D192" t="s">
         <v>63</v>
@@ -3268,7 +3268,7 @@
         <v>48</v>
       </c>
       <c r="C193">
-        <v>62.09</v>
+        <v>-62.09</v>
       </c>
       <c r="D193" t="s">
         <v>65</v>
@@ -3296,7 +3296,7 @@
         <v>55</v>
       </c>
       <c r="C195">
-        <v>87.87</v>
+        <v>-87.87</v>
       </c>
       <c r="D195" t="s">
         <v>65</v>
@@ -3310,7 +3310,7 @@
         <v>50</v>
       </c>
       <c r="C196">
-        <v>62.96</v>
+        <v>-62.96</v>
       </c>
       <c r="D196" t="s">
         <v>63</v>
@@ -3324,7 +3324,7 @@
         <v>41</v>
       </c>
       <c r="C197">
-        <v>23.66</v>
+        <v>-23.66</v>
       </c>
       <c r="D197" t="s">
         <v>61</v>
@@ -3338,7 +3338,7 @@
         <v>45</v>
       </c>
       <c r="C198">
-        <v>266.59</v>
+        <v>-266.59</v>
       </c>
       <c r="D198" t="s">
         <v>64</v>
@@ -3352,7 +3352,7 @@
         <v>41</v>
       </c>
       <c r="C199">
-        <v>95.45999999999999</v>
+        <v>-95.45999999999999</v>
       </c>
       <c r="D199" t="s">
         <v>61</v>
@@ -3366,7 +3366,7 @@
         <v>49</v>
       </c>
       <c r="C200">
-        <v>19.2</v>
+        <v>-19.2</v>
       </c>
       <c r="D200" t="s">
         <v>58</v>
@@ -3380,7 +3380,7 @@
         <v>50</v>
       </c>
       <c r="C201">
-        <v>206.32</v>
+        <v>-206.32</v>
       </c>
       <c r="D201" t="s">
         <v>63</v>
